--- a/data/sars/alaska/tables/Alaska_2001_Appendix2.xlsx
+++ b/data/sars/alaska/tables/Alaska_2001_Appendix2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/alaska/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41800990-E177-C64F-9673-8FCCB62827BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4630A51D-4297-0446-8DD6-5430A51AB2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="21900" xr2:uid="{4567688A-11AE-C84E-B4A5-C2C3C2D14B01}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="67">
   <si>
     <t>Alaska</t>
   </si>
@@ -215,13 +215,19 @@
   </si>
   <si>
     <t>W.U. S.</t>
+  </si>
+  <si>
+    <t>revised_yn</t>
+  </si>
+  <si>
+    <t>yes</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -363,6 +369,20 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
@@ -710,7 +730,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -722,6 +742,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1099,17 +1128,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08544619-115F-E74A-ADA0-626BF669AB9A}">
-  <dimension ref="A1:O33"/>
+  <dimension ref="A1:P33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.5" style="1" customWidth="1"/>
     <col min="2" max="2" width="23.83203125" style="1" customWidth="1"/>
-    <col min="3" max="14" width="10.83203125" style="1"/>
-    <col min="15" max="15" width="10.83203125" style="2"/>
-    <col min="16" max="16384" width="10.83203125" style="1"/>
+    <col min="3" max="15" width="10.83203125" style="1"/>
+    <col min="16" max="16" width="10.83203125" style="2"/>
+    <col min="17" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>49</v>
       </c>
@@ -1152,11 +1181,14 @@
       <c r="N1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>22</v>
       </c>
@@ -1187,43 +1219,46 @@
       <c r="N2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I3" s="1">
+      <c r="B3" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5">
         <v>0.06</v>
       </c>
-      <c r="J3" s="1">
+      <c r="J3" s="5">
         <v>0.5</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L3" s="1">
-        <v>1</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="N3" s="1" t="s">
+      <c r="K3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="N3" s="5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O3" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -1267,7 +1302,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -1311,7 +1346,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -1354,11 +1389,11 @@
       <c r="N6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="O6" s="4" t="s">
+      <c r="P6" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -1401,87 +1436,93 @@
       <c r="N7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="O7" s="4" t="s">
+      <c r="P7" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="5">
         <v>435</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="5">
         <v>0.23</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" s="5">
         <v>0.23</v>
       </c>
-      <c r="H8" s="1">
+      <c r="H8" s="5">
         <v>360</v>
       </c>
-      <c r="I8" s="1">
+      <c r="I8" s="5">
         <v>0.02</v>
       </c>
-      <c r="J8" s="1">
+      <c r="J8" s="5">
         <v>0.3</v>
       </c>
-      <c r="K8" s="1">
+      <c r="K8" s="5">
         <v>2.2000000000000002</v>
       </c>
-      <c r="L8" s="1">
-        <v>0</v>
-      </c>
-      <c r="M8" s="1">
-        <v>0</v>
-      </c>
-      <c r="N8" s="1" t="s">
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
+      <c r="O8" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="6">
         <v>8200</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="5">
         <v>6.9000000000000006E-2</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" s="5">
         <v>6.9000000000000006E-2</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="6">
         <v>7738</v>
       </c>
-      <c r="I9" s="1">
+      <c r="I9" s="5">
         <v>0.02</v>
       </c>
-      <c r="J9" s="1">
+      <c r="J9" s="5">
         <v>0.5</v>
       </c>
-      <c r="K9" s="1">
+      <c r="K9" s="5">
         <v>77</v>
       </c>
-      <c r="L9" s="1">
-        <v>0</v>
-      </c>
-      <c r="M9" s="1">
+      <c r="L9" s="5">
+        <v>0</v>
+      </c>
+      <c r="M9" s="5">
         <v>54</v>
       </c>
-      <c r="N9" s="1" t="s">
+      <c r="N9" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O9" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>23</v>
       </c>
@@ -1513,7 +1554,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>24</v>
       </c>
@@ -1551,39 +1592,42 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
+    <row r="12" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I12" s="1">
+      <c r="C12" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I12" s="5">
         <v>0.02</v>
       </c>
-      <c r="J12" s="1">
+      <c r="J12" s="5">
         <v>0.1</v>
       </c>
-      <c r="K12" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L12" s="1">
-        <v>0</v>
-      </c>
-      <c r="M12" s="1">
-        <v>0</v>
-      </c>
-      <c r="N12" s="1" t="s">
+      <c r="K12" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O12" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
@@ -1621,7 +1665,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>25</v>
       </c>
@@ -1664,11 +1708,11 @@
       <c r="N14" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="4" t="s">
+      <c r="P14" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>25</v>
       </c>
@@ -1712,7 +1756,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>25</v>
       </c>
@@ -1756,7 +1800,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>11</v>
       </c>
@@ -1800,7 +1844,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>11</v>
       </c>
@@ -1844,7 +1888,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>11</v>
       </c>
@@ -1888,226 +1932,244 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
+    <row r="20" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20" s="5">
         <v>394</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D20" s="5">
         <v>8.4000000000000005E-2</v>
       </c>
-      <c r="G20" s="1">
+      <c r="G20" s="5">
         <v>8.4000000000000005E-2</v>
       </c>
-      <c r="H20" s="1">
+      <c r="H20" s="5">
         <v>367</v>
       </c>
-      <c r="I20" s="1">
+      <c r="I20" s="5">
         <v>0.02</v>
       </c>
-      <c r="J20" s="1">
+      <c r="J20" s="5">
         <v>0.1</v>
       </c>
-      <c r="K20" s="1">
+      <c r="K20" s="5">
         <v>0.7</v>
       </c>
-      <c r="L20" s="1">
+      <c r="L20" s="5">
         <v>0.6</v>
       </c>
-      <c r="M20" s="1">
-        <v>0</v>
-      </c>
-      <c r="N20" s="1" t="s">
+      <c r="M20" s="5">
+        <v>0</v>
+      </c>
+      <c r="N20" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
+      <c r="O20" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="6">
         <v>4005</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D21" s="5">
         <v>9.5000000000000001E-2</v>
       </c>
-      <c r="G21" s="1">
+      <c r="G21" s="5">
         <v>9.5000000000000001E-2</v>
       </c>
-      <c r="H21" s="3">
+      <c r="H21" s="6">
         <v>3698</v>
       </c>
-      <c r="I21" s="1">
+      <c r="I21" s="5">
         <v>0.02</v>
       </c>
-      <c r="J21" s="1">
+      <c r="J21" s="5">
         <v>0.1</v>
       </c>
-      <c r="K21" s="1">
+      <c r="K21" s="5">
         <v>7.4</v>
       </c>
-      <c r="L21" s="1">
+      <c r="L21" s="5">
         <v>3.5</v>
       </c>
-      <c r="M21" s="1">
-        <v>0</v>
-      </c>
-      <c r="N21" s="1" t="s">
+      <c r="M21" s="5">
+        <v>0</v>
+      </c>
+      <c r="N21" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
+      <c r="O21" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C22" s="5">
         <v>723</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G22" s="1" t="s">
+      <c r="D22" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G22" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H22" s="1">
+      <c r="H22" s="5">
         <v>723</v>
       </c>
-      <c r="I22" s="1">
+      <c r="I22" s="5">
         <v>0.02</v>
       </c>
-      <c r="J22" s="1">
+      <c r="J22" s="5">
         <v>0.5</v>
       </c>
-      <c r="K22" s="1">
+      <c r="K22" s="5">
         <v>7.2</v>
       </c>
-      <c r="L22" s="1">
+      <c r="L22" s="5">
         <v>1.4</v>
       </c>
-      <c r="M22" s="1">
-        <v>0</v>
-      </c>
-      <c r="N22" s="1" t="s">
+      <c r="M22" s="5">
+        <v>0</v>
+      </c>
+      <c r="N22" s="5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A23" s="1" t="s">
+      <c r="O22" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I23" s="1">
+      <c r="B23" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I23" s="5">
         <v>0.02</v>
       </c>
-      <c r="J23" s="1">
+      <c r="J23" s="5">
         <v>0.5</v>
       </c>
-      <c r="K23" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L23" s="1">
-        <v>0</v>
-      </c>
-      <c r="M23" s="1">
-        <v>0</v>
-      </c>
-      <c r="N23" s="1" t="s">
+      <c r="K23" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L23" s="5">
+        <v>0</v>
+      </c>
+      <c r="M23" s="5">
+        <v>0</v>
+      </c>
+      <c r="N23" s="5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A24" s="1" t="s">
+      <c r="O23" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I24" s="1">
+      <c r="C24" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I24" s="5">
         <v>0.02</v>
       </c>
-      <c r="J24" s="1">
+      <c r="J24" s="5">
         <v>0.1</v>
       </c>
-      <c r="K24" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L24" s="1">
-        <v>0</v>
-      </c>
-      <c r="M24" s="1">
-        <v>0</v>
-      </c>
-      <c r="N24" s="1" t="s">
+      <c r="K24" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L24" s="5">
+        <v>0</v>
+      </c>
+      <c r="M24" s="5">
+        <v>0</v>
+      </c>
+      <c r="N24" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
+      <c r="O24" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E25" s="1">
+      <c r="E25" s="5">
         <v>4.4749999999999996</v>
       </c>
-      <c r="F25" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G25" s="1">
+      <c r="F25" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G25" s="5">
         <v>0.2</v>
       </c>
-      <c r="H25" s="3">
+      <c r="H25" s="6">
         <v>832798</v>
       </c>
-      <c r="I25" s="1">
+      <c r="I25" s="5">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="J25" s="1">
+      <c r="J25" s="5">
         <v>0.5</v>
       </c>
-      <c r="K25" s="3">
+      <c r="K25" s="6">
         <v>17905</v>
       </c>
-      <c r="L25" s="1">
+      <c r="L25" s="5">
         <v>15</v>
       </c>
-      <c r="M25" s="3">
+      <c r="M25" s="6">
         <v>1495</v>
       </c>
-      <c r="N25" s="1" t="s">
+      <c r="N25" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O25" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>28</v>
       </c>
@@ -2139,71 +2201,77 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A27" s="1" t="s">
+    <row r="27" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I27" s="1">
+      <c r="B27" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I27" s="5">
         <v>0.06</v>
       </c>
-      <c r="J27" s="1">
+      <c r="J27" s="5">
         <v>0.5</v>
       </c>
-      <c r="K27" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L27" s="1">
-        <v>1</v>
-      </c>
-      <c r="M27" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="N27" s="1" t="s">
+      <c r="K27" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L27" s="5">
+        <v>1</v>
+      </c>
+      <c r="M27" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="N27" s="5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A28" s="1" t="s">
+      <c r="O27" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I28" s="1">
+      <c r="B28" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I28" s="5">
         <v>0.06</v>
       </c>
-      <c r="J28" s="1">
+      <c r="J28" s="5">
         <v>0.5</v>
       </c>
-      <c r="K28" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L28" s="1">
-        <v>0</v>
-      </c>
-      <c r="M28" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="N28" s="1" t="s">
+      <c r="K28" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L28" s="5">
+        <v>0</v>
+      </c>
+      <c r="M28" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="N28" s="5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O28" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>18</v>
       </c>
@@ -2235,42 +2303,45 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A30" s="1" t="s">
+    <row r="30" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I30" s="1">
+      <c r="B30" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I30" s="5">
         <v>0.06</v>
       </c>
-      <c r="J30" s="1">
+      <c r="J30" s="5">
         <v>0.5</v>
       </c>
-      <c r="K30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L30" s="1">
+      <c r="K30" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L30" s="5">
         <v>3</v>
       </c>
-      <c r="M30" s="1" t="s">
+      <c r="M30" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="N30" s="1" t="s">
+      <c r="N30" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="O30" s="2" t="s">
+      <c r="O30" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="P30" s="5" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>29</v>
       </c>
@@ -2302,71 +2373,77 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A32" s="1" t="s">
+    <row r="32" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="6">
         <v>31005</v>
       </c>
-      <c r="H32" s="3">
+      <c r="H32" s="6">
         <v>31005</v>
       </c>
-      <c r="I32" s="1">
+      <c r="I32" s="5">
         <v>0.06</v>
       </c>
-      <c r="J32" s="1">
+      <c r="J32" s="5">
         <v>0.75</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="6">
         <v>1395</v>
       </c>
-      <c r="L32" s="1">
+      <c r="L32" s="5">
         <v>2.7</v>
       </c>
-      <c r="M32" s="1">
-        <v>0</v>
-      </c>
-      <c r="N32" s="1" t="s">
+      <c r="M32" s="5">
+        <v>0</v>
+      </c>
+      <c r="N32" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="O32" s="4" t="s">
+      <c r="O32" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="P32" s="7" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A33" s="1" t="s">
+    <row r="33" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C33" s="3">
+      <c r="C33" s="6">
         <v>34600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="H33" s="6">
         <v>34600</v>
       </c>
-      <c r="I33" s="1">
+      <c r="I33" s="5">
         <v>0.06</v>
       </c>
-      <c r="J33" s="1">
+      <c r="J33" s="5">
         <v>0.1</v>
       </c>
-      <c r="K33" s="3">
+      <c r="K33" s="6">
         <v>208</v>
       </c>
-      <c r="L33" s="1">
+      <c r="L33" s="5">
         <v>28.3</v>
       </c>
-      <c r="M33" s="1">
+      <c r="M33" s="5">
         <v>353</v>
       </c>
-      <c r="N33" s="1" t="s">
+      <c r="N33" s="5" t="s">
         <v>7</v>
+      </c>
+      <c r="O33" s="5" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
